--- a/sims/BURR2_FULL_LOOP_v1.xlsx
+++ b/sims/BURR2_FULL_LOOP_v1.xlsx
@@ -38,7 +38,7 @@
     <numFmt numFmtId="173" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="174" formatCode="0.000000000000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +73,11 @@
     <font>
       <b val="1"/>
       <color rgb="00C53030"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C53030"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -153,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -277,6 +282,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -642,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -660,7 +667,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -945,7 +951,6 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -1037,7 +1042,6 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
@@ -1183,38 +1187,18 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>QN</t>
+          <t>QN_volwtd</t>
         </is>
       </c>
       <c r="B39" s="9" t="n">
         <v>0.025</v>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>average trade size as fraction of pool</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
+      <c r="C39" s="45" t="inlineStr">
+        <is>
+          <t>VOLUME-WEIGHTED avg trade size (fraction of pool). NOT the plain average: a few whales push this UP a lot. Revenue tracks THIS number.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
@@ -1577,10 +1561,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1636,6 +1621,11 @@
           <t>-k (must match)</t>
         </is>
       </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>Gtilde (per strike)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
@@ -1673,6 +1663,7 @@
         <f>-A4</f>
         <v/>
       </c>
+      <c r="J4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
@@ -1710,6 +1701,10 @@
         <f>-A5</f>
         <v/>
       </c>
+      <c r="J5" s="18">
+        <f>IFERROR(ABS(2*((A6-A5)*F4-(A6-A4)*F5+(A5-A4)*F6)/((A5-A4)*(A6-A5)*(A6-A4))*(1+A5)^2/MAX(F5,0.000001)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
@@ -1747,6 +1742,10 @@
         <f>-A6</f>
         <v/>
       </c>
+      <c r="J6" s="18">
+        <f>IFERROR(ABS(2*((A7-A6)*F5-(A7-A5)*F6+(A6-A5)*F7)/((A6-A5)*(A7-A6)*(A7-A5))*(1+A6)^2/MAX(F6,0.000001)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -1784,6 +1783,10 @@
         <f>-A7</f>
         <v/>
       </c>
+      <c r="J7" s="18">
+        <f>IFERROR(ABS(2*((A8-A7)*F6-(A8-A6)*F7+(A7-A6)*F8)/((A7-A6)*(A8-A7)*(A8-A6))*(1+A7)^2/MAX(F7,0.000001)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
@@ -1821,6 +1824,10 @@
         <f>-A8</f>
         <v/>
       </c>
+      <c r="J8" s="18">
+        <f>IFERROR(ABS(2*((A9-A8)*F7-(A9-A7)*F8+(A8-A7)*F9)/((A8-A7)*(A9-A8)*(A9-A7))*(1+A8)^2/MAX(F8,0.000001)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
@@ -1858,6 +1865,10 @@
         <f>-A9</f>
         <v/>
       </c>
+      <c r="J9" s="18">
+        <f>IFERROR(ABS(2*((A10-A9)*F8-(A10-A8)*F9+(A9-A8)*F10)/((A9-A8)*(A10-A9)*(A10-A8))*(1+A9)^2/MAX(F9,0.000001)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
@@ -1895,6 +1906,10 @@
         <f>-A10</f>
         <v/>
       </c>
+      <c r="J10" s="18">
+        <f>IFERROR(ABS(2*((A11-A10)*F9-(A11-A9)*F10+(A10-A9)*F11)/((A10-A9)*(A11-A10)*(A11-A9))*(1+A10)^2/MAX(F10,0.000001)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
@@ -1932,6 +1947,10 @@
         <f>-A11</f>
         <v/>
       </c>
+      <c r="J11" s="18">
+        <f>IFERROR(ABS(2*((A12-A11)*F10-(A12-A10)*F11+(A11-A10)*F12)/((A11-A10)*(A12-A11)*(A12-A10))*(1+A11)^2/MAX(F11,0.000001)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
@@ -1969,6 +1988,10 @@
         <f>-A12</f>
         <v/>
       </c>
+      <c r="J12" s="18">
+        <f>IFERROR(ABS(2*((A13-A12)*F11-(A13-A11)*F12+(A12-A11)*F13)/((A12-A11)*(A13-A12)*(A13-A11))*(1+A12)^2/MAX(F12,0.000001)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
@@ -2006,6 +2029,10 @@
         <f>-A13</f>
         <v/>
       </c>
+      <c r="J13" s="18">
+        <f>IFERROR(ABS(2*((A14-A13)*F12-(A14-A12)*F13+(A13-A12)*F14)/((A13-A12)*(A14-A13)*(A14-A12))*(1+A13)^2/MAX(F13,0.000001)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="n">
@@ -2042,6 +2069,34 @@
       <c r="I14" s="16">
         <f>-A14</f>
         <v/>
+      </c>
+      <c r="J14" s="18" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>mean Gtilde</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="J17" s="46">
+        <f>AVERAGE(J5:J13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Gtilde uses the UNEVEN-GRID 2nd-derivative formula (the strike grid is not equally spaced).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>It rises with |k| on the OTM side: wing inventory is far more expensive to carry than ATM.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2501,10 +2556,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2814,6 +2874,279 @@
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Closed form suffices ONLY for depth-only heterogeneity. Posted spread or shape =&gt; the ladder is load-bearing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>C. LADDER ORDER IS NOT FIXED — it must be re-sorted per strike</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>strike k</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>cheapest LP here</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>h of cheapest</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>order changes?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18">
+        <f>'1_Curve'!A4</f>
+        <v/>
+      </c>
+      <c r="B24" s="30">
+        <f>INDEX({"LP-C","LP-B","LP-A"},MATCH(MIN('0_Inputs'!$C$25*(1+ABS(A24)*0),'0_Inputs'!$C$26*(1+ABS(A24)*1),'0_Inputs'!$C$27*(1+ABS(A24)*3)),{'0_Inputs'!$C$25*(1+ABS(A24)*0),'0_Inputs'!$C$26*(1+ABS(A24)*1),'0_Inputs'!$C$27*(1+ABS(A24)*3)},0))</f>
+        <v/>
+      </c>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="20">
+        <f>MIN('0_Inputs'!$C$25*(1+ABS(A24)*0),'0_Inputs'!$C$26*(1+ABS(A24)*1),'0_Inputs'!$C$27*(1+ABS(A24)*3))</f>
+        <v/>
+      </c>
+      <c r="F24" s="30">
+        <f>IF(B24=B$24,"same","CHANGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18">
+        <f>'1_Curve'!A5</f>
+        <v/>
+      </c>
+      <c r="B25" s="30">
+        <f>INDEX({"LP-C","LP-B","LP-A"},MATCH(MIN('0_Inputs'!$C$25*(1+ABS(A25)*0),'0_Inputs'!$C$26*(1+ABS(A25)*1),'0_Inputs'!$C$27*(1+ABS(A25)*3)),{'0_Inputs'!$C$25*(1+ABS(A25)*0),'0_Inputs'!$C$26*(1+ABS(A25)*1),'0_Inputs'!$C$27*(1+ABS(A25)*3)},0))</f>
+        <v/>
+      </c>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="30" t="n"/>
+      <c r="E25" s="20">
+        <f>MIN('0_Inputs'!$C$25*(1+ABS(A25)*0),'0_Inputs'!$C$26*(1+ABS(A25)*1),'0_Inputs'!$C$27*(1+ABS(A25)*3))</f>
+        <v/>
+      </c>
+      <c r="F25" s="30">
+        <f>IF(B25=B$24,"same","CHANGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18">
+        <f>'1_Curve'!A6</f>
+        <v/>
+      </c>
+      <c r="B26" s="30">
+        <f>INDEX({"LP-C","LP-B","LP-A"},MATCH(MIN('0_Inputs'!$C$25*(1+ABS(A26)*0),'0_Inputs'!$C$26*(1+ABS(A26)*1),'0_Inputs'!$C$27*(1+ABS(A26)*3)),{'0_Inputs'!$C$25*(1+ABS(A26)*0),'0_Inputs'!$C$26*(1+ABS(A26)*1),'0_Inputs'!$C$27*(1+ABS(A26)*3)},0))</f>
+        <v/>
+      </c>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="20">
+        <f>MIN('0_Inputs'!$C$25*(1+ABS(A26)*0),'0_Inputs'!$C$26*(1+ABS(A26)*1),'0_Inputs'!$C$27*(1+ABS(A26)*3))</f>
+        <v/>
+      </c>
+      <c r="F26" s="30">
+        <f>IF(B26=B$24,"same","CHANGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18">
+        <f>'1_Curve'!A7</f>
+        <v/>
+      </c>
+      <c r="B27" s="30">
+        <f>INDEX({"LP-C","LP-B","LP-A"},MATCH(MIN('0_Inputs'!$C$25*(1+ABS(A27)*0),'0_Inputs'!$C$26*(1+ABS(A27)*1),'0_Inputs'!$C$27*(1+ABS(A27)*3)),{'0_Inputs'!$C$25*(1+ABS(A27)*0),'0_Inputs'!$C$26*(1+ABS(A27)*1),'0_Inputs'!$C$27*(1+ABS(A27)*3)},0))</f>
+        <v/>
+      </c>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="20">
+        <f>MIN('0_Inputs'!$C$25*(1+ABS(A27)*0),'0_Inputs'!$C$26*(1+ABS(A27)*1),'0_Inputs'!$C$27*(1+ABS(A27)*3))</f>
+        <v/>
+      </c>
+      <c r="F27" s="30">
+        <f>IF(B27=B$24,"same","CHANGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18">
+        <f>'1_Curve'!A8</f>
+        <v/>
+      </c>
+      <c r="B28" s="30">
+        <f>INDEX({"LP-C","LP-B","LP-A"},MATCH(MIN('0_Inputs'!$C$25*(1+ABS(A28)*0),'0_Inputs'!$C$26*(1+ABS(A28)*1),'0_Inputs'!$C$27*(1+ABS(A28)*3)),{'0_Inputs'!$C$25*(1+ABS(A28)*0),'0_Inputs'!$C$26*(1+ABS(A28)*1),'0_Inputs'!$C$27*(1+ABS(A28)*3)},0))</f>
+        <v/>
+      </c>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="30" t="n"/>
+      <c r="E28" s="20">
+        <f>MIN('0_Inputs'!$C$25*(1+ABS(A28)*0),'0_Inputs'!$C$26*(1+ABS(A28)*1),'0_Inputs'!$C$27*(1+ABS(A28)*3))</f>
+        <v/>
+      </c>
+      <c r="F28" s="30">
+        <f>IF(B28=B$24,"same","CHANGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18">
+        <f>'1_Curve'!A9</f>
+        <v/>
+      </c>
+      <c r="B29" s="30">
+        <f>INDEX({"LP-C","LP-B","LP-A"},MATCH(MIN('0_Inputs'!$C$25*(1+ABS(A29)*0),'0_Inputs'!$C$26*(1+ABS(A29)*1),'0_Inputs'!$C$27*(1+ABS(A29)*3)),{'0_Inputs'!$C$25*(1+ABS(A29)*0),'0_Inputs'!$C$26*(1+ABS(A29)*1),'0_Inputs'!$C$27*(1+ABS(A29)*3)},0))</f>
+        <v/>
+      </c>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="30" t="n"/>
+      <c r="E29" s="20">
+        <f>MIN('0_Inputs'!$C$25*(1+ABS(A29)*0),'0_Inputs'!$C$26*(1+ABS(A29)*1),'0_Inputs'!$C$27*(1+ABS(A29)*3))</f>
+        <v/>
+      </c>
+      <c r="F29" s="30">
+        <f>IF(B29=B$24,"same","CHANGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18">
+        <f>'1_Curve'!A10</f>
+        <v/>
+      </c>
+      <c r="B30" s="30">
+        <f>INDEX({"LP-C","LP-B","LP-A"},MATCH(MIN('0_Inputs'!$C$25*(1+ABS(A30)*0),'0_Inputs'!$C$26*(1+ABS(A30)*1),'0_Inputs'!$C$27*(1+ABS(A30)*3)),{'0_Inputs'!$C$25*(1+ABS(A30)*0),'0_Inputs'!$C$26*(1+ABS(A30)*1),'0_Inputs'!$C$27*(1+ABS(A30)*3)},0))</f>
+        <v/>
+      </c>
+      <c r="C30" s="30" t="n"/>
+      <c r="D30" s="30" t="n"/>
+      <c r="E30" s="20">
+        <f>MIN('0_Inputs'!$C$25*(1+ABS(A30)*0),'0_Inputs'!$C$26*(1+ABS(A30)*1),'0_Inputs'!$C$27*(1+ABS(A30)*3))</f>
+        <v/>
+      </c>
+      <c r="F30" s="30">
+        <f>IF(B30=B$24,"same","CHANGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18">
+        <f>'1_Curve'!A11</f>
+        <v/>
+      </c>
+      <c r="B31" s="30">
+        <f>INDEX({"LP-C","LP-B","LP-A"},MATCH(MIN('0_Inputs'!$C$25*(1+ABS(A31)*0),'0_Inputs'!$C$26*(1+ABS(A31)*1),'0_Inputs'!$C$27*(1+ABS(A31)*3)),{'0_Inputs'!$C$25*(1+ABS(A31)*0),'0_Inputs'!$C$26*(1+ABS(A31)*1),'0_Inputs'!$C$27*(1+ABS(A31)*3)},0))</f>
+        <v/>
+      </c>
+      <c r="C31" s="30" t="n"/>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="20">
+        <f>MIN('0_Inputs'!$C$25*(1+ABS(A31)*0),'0_Inputs'!$C$26*(1+ABS(A31)*1),'0_Inputs'!$C$27*(1+ABS(A31)*3))</f>
+        <v/>
+      </c>
+      <c r="F31" s="30">
+        <f>IF(B31=B$24,"same","CHANGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18">
+        <f>'1_Curve'!A12</f>
+        <v/>
+      </c>
+      <c r="B32" s="30">
+        <f>INDEX({"LP-C","LP-B","LP-A"},MATCH(MIN('0_Inputs'!$C$25*(1+ABS(A32)*0),'0_Inputs'!$C$26*(1+ABS(A32)*1),'0_Inputs'!$C$27*(1+ABS(A32)*3)),{'0_Inputs'!$C$25*(1+ABS(A32)*0),'0_Inputs'!$C$26*(1+ABS(A32)*1),'0_Inputs'!$C$27*(1+ABS(A32)*3)},0))</f>
+        <v/>
+      </c>
+      <c r="C32" s="30" t="n"/>
+      <c r="D32" s="30" t="n"/>
+      <c r="E32" s="20">
+        <f>MIN('0_Inputs'!$C$25*(1+ABS(A32)*0),'0_Inputs'!$C$26*(1+ABS(A32)*1),'0_Inputs'!$C$27*(1+ABS(A32)*3))</f>
+        <v/>
+      </c>
+      <c r="F32" s="30">
+        <f>IF(B32=B$24,"same","CHANGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18">
+        <f>'1_Curve'!A13</f>
+        <v/>
+      </c>
+      <c r="B33" s="30">
+        <f>INDEX({"LP-C","LP-B","LP-A"},MATCH(MIN('0_Inputs'!$C$25*(1+ABS(A33)*0),'0_Inputs'!$C$26*(1+ABS(A33)*1),'0_Inputs'!$C$27*(1+ABS(A33)*3)),{'0_Inputs'!$C$25*(1+ABS(A33)*0),'0_Inputs'!$C$26*(1+ABS(A33)*1),'0_Inputs'!$C$27*(1+ABS(A33)*3)},0))</f>
+        <v/>
+      </c>
+      <c r="C33" s="30" t="n"/>
+      <c r="D33" s="30" t="n"/>
+      <c r="E33" s="20">
+        <f>MIN('0_Inputs'!$C$25*(1+ABS(A33)*0),'0_Inputs'!$C$26*(1+ABS(A33)*1),'0_Inputs'!$C$27*(1+ABS(A33)*3))</f>
+        <v/>
+      </c>
+      <c r="F33" s="30">
+        <f>IF(B33=B$24,"same","CHANGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18">
+        <f>'1_Curve'!A14</f>
+        <v/>
+      </c>
+      <c r="B34" s="30">
+        <f>INDEX({"LP-C","LP-B","LP-A"},MATCH(MIN('0_Inputs'!$C$25*(1+ABS(A34)*0),'0_Inputs'!$C$26*(1+ABS(A34)*1),'0_Inputs'!$C$27*(1+ABS(A34)*3)),{'0_Inputs'!$C$25*(1+ABS(A34)*0),'0_Inputs'!$C$26*(1+ABS(A34)*1),'0_Inputs'!$C$27*(1+ABS(A34)*3)},0))</f>
+        <v/>
+      </c>
+      <c r="C34" s="30" t="n"/>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="20">
+        <f>MIN('0_Inputs'!$C$25*(1+ABS(A34)*0),'0_Inputs'!$C$26*(1+ABS(A34)*1),'0_Inputs'!$C$27*(1+ABS(A34)*3))</f>
+        <v/>
+      </c>
+      <c r="F34" s="30">
+        <f>IF(B34=B$24,"same","CHANGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Each LP's posted spread can vary with strike (h_i(k)). When it does, the cheapest LP CHANGES by strike,</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>so the fill ladder must be re-sorted at every strike — a single fixed order is wrong. Column F flags where it changes.</t>
         </is>
       </c>
     </row>
@@ -3677,7 +4010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3820,15 +4153,15 @@
         </is>
       </c>
       <c r="B8" s="18">
-        <f>5.76</f>
+        <f>'1_Curve'!$J$17</f>
         <v/>
       </c>
       <c r="C8" s="18">
-        <f>5.76</f>
+        <f>'1_Curve'!$J$17</f>
         <v/>
       </c>
       <c r="D8" s="18">
-        <f>5.76</f>
+        <f>'1_Curve'!$J$17</f>
         <v/>
       </c>
       <c r="E8" s="16">
@@ -3931,7 +4264,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Gtilde=5.76 is the measured Burr-2 curvature per unit value (mean over strikes); it RISES with |k|.</t>
+          <t>Gtilde now READ LIVE from 1_Curve!J17 (mean of the per-strike column), not hard-coded. It rises with |k|.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>NOTE: an LP concentrated in the wings faces a HIGHER Gtilde than this mean; per-LP strike mix is the next refinement.</t>
         </is>
       </c>
     </row>

--- a/sims/BURR2_FULL_LOOP_v1.xlsx
+++ b/sims/BURR2_FULL_LOOP_v1.xlsx
@@ -17,6 +17,7 @@
     <sheet name="7_Margin" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="8_LP_Econ" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="9_CHECKS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10_Viability" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -37,6 +38,7 @@
     <numFmt numFmtId="172" formatCode="0.0000000000"/>
     <numFmt numFmtId="173" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="174" formatCode="0.000000000000"/>
+    <numFmt numFmtId="175" formatCode="0&quot; bps&quot;"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -158,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -284,10 +286,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6F6D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FED7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -649,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -667,6 +694,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -951,6 +979,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -1042,6 +1071,7 @@
         <v>250000</v>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
@@ -1199,6 +1229,26 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
@@ -1555,6 +1605,332 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VIABILITY — fee x turnover (integral convention: revenue = fee x volume)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>gamma bleed / yr (per unit book value)</t>
+        </is>
+      </c>
+      <c r="B3" s="47">
+        <f>0.5*'1_Curve'!$J$17*'0_Inputs'!$B$37^2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>NET (revenue - bleed), x book value/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>fee (bps) \ turnover/day</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="B7" s="18">
+        <f>$A7/10000*B$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="C7" s="18">
+        <f>$A7/10000*C$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="D7" s="18">
+        <f>$A7/10000*D$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="E7" s="18">
+        <f>$A7/10000*E$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="F7" s="18">
+        <f>$A7/10000*F$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="18">
+        <f>$A7/10000*G$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="18">
+        <f>$A7/10000*H$6*365-$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="B8" s="18">
+        <f>$A8/10000*B$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="C8" s="18">
+        <f>$A8/10000*C$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="D8" s="18">
+        <f>$A8/10000*D$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="E8" s="18">
+        <f>$A8/10000*E$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="F8" s="18">
+        <f>$A8/10000*F$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="18">
+        <f>$A8/10000*G$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="18">
+        <f>$A8/10000*H$6*365-$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="49" t="n">
+        <v>50</v>
+      </c>
+      <c r="B9" s="18">
+        <f>$A9/10000*B$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="C9" s="18">
+        <f>$A9/10000*C$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="D9" s="18">
+        <f>$A9/10000*D$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="E9" s="18">
+        <f>$A9/10000*E$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="F9" s="18">
+        <f>$A9/10000*F$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="18">
+        <f>$A9/10000*G$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="18">
+        <f>$A9/10000*H$6*365-$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="n">
+        <v>75</v>
+      </c>
+      <c r="B10" s="18">
+        <f>$A10/10000*B$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="C10" s="18">
+        <f>$A10/10000*C$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="D10" s="18">
+        <f>$A10/10000*D$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="E10" s="18">
+        <f>$A10/10000*E$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="F10" s="18">
+        <f>$A10/10000*F$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="18">
+        <f>$A10/10000*G$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="18">
+        <f>$A10/10000*H$6*365-$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" s="18">
+        <f>$A11/10000*B$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="C11" s="18">
+        <f>$A11/10000*C$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="D11" s="18">
+        <f>$A11/10000*D$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="E11" s="18">
+        <f>$A11/10000*E$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="F11" s="18">
+        <f>$A11/10000*F$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="18">
+        <f>$A11/10000*G$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="18">
+        <f>$A11/10000*H$6*365-$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="n">
+        <v>150</v>
+      </c>
+      <c r="B12" s="18">
+        <f>$A12/10000*B$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="C12" s="18">
+        <f>$A12/10000*C$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="D12" s="18">
+        <f>$A12/10000*D$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="E12" s="18">
+        <f>$A12/10000*E$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="F12" s="18">
+        <f>$A12/10000*F$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="18">
+        <f>$A12/10000*G$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="18">
+        <f>$A12/10000*H$6*365-$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="n">
+        <v>200</v>
+      </c>
+      <c r="B13" s="18">
+        <f>$A13/10000*B$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="C13" s="18">
+        <f>$A13/10000*C$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="D13" s="18">
+        <f>$A13/10000*D$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="E13" s="18">
+        <f>$A13/10000*E$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="F13" s="18">
+        <f>$A13/10000*F$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="18">
+        <f>$A13/10000*G$6*365-$B$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="18">
+        <f>$A13/10000*H$6*365-$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>green = LP profitable. Break-even fee at a given turnover: fee = bleed/(turnover x 365).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>TODAY: 30bps at 0.3x/day = deep red. You need ~90bps at 0.3x, or ~0.9x/day at 30bps.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B7:H13">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2113,7 +2489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2122,7 +2498,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TWO-SIDED QUOTE — impact (size-proportional, irreversible) + per-LP POSTED spread</t>
+          <t>TWO-SIDED QUOTE — CONTINUOUS (integral) execution: trader pays the AVERAGE along the path</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2515,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>impact s</t>
+          <t>impact s_full</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -2149,7 +2525,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>half-spread</t>
+          <t>effective half-spread (s_full/2)</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2178,7 +2554,7 @@
         <v/>
       </c>
       <c r="C4" s="19">
-        <f>0.5*'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B4,0.000000001)</f>
+        <f>'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B4,0.000000001)</f>
         <v/>
       </c>
       <c r="D4" s="20">
@@ -2186,7 +2562,7 @@
         <v/>
       </c>
       <c r="E4" s="19">
-        <f>C4+D4</f>
+        <f>C4/2+D4</f>
         <v/>
       </c>
       <c r="F4" s="16">
@@ -2212,7 +2588,7 @@
         <v/>
       </c>
       <c r="C5" s="19">
-        <f>0.5*'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B5,0.000000001)</f>
+        <f>'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B5,0.000000001)</f>
         <v/>
       </c>
       <c r="D5" s="20">
@@ -2220,7 +2596,7 @@
         <v/>
       </c>
       <c r="E5" s="19">
-        <f>C5+D5</f>
+        <f>C5/2+D5</f>
         <v/>
       </c>
       <c r="F5" s="16">
@@ -2246,7 +2622,7 @@
         <v/>
       </c>
       <c r="C6" s="19">
-        <f>0.5*'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B6,0.000000001)</f>
+        <f>'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B6,0.000000001)</f>
         <v/>
       </c>
       <c r="D6" s="20">
@@ -2254,7 +2630,7 @@
         <v/>
       </c>
       <c r="E6" s="19">
-        <f>C6+D6</f>
+        <f>C6/2+D6</f>
         <v/>
       </c>
       <c r="F6" s="16">
@@ -2280,7 +2656,7 @@
         <v/>
       </c>
       <c r="C7" s="19">
-        <f>0.5*'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B7,0.000000001)</f>
+        <f>'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B7,0.000000001)</f>
         <v/>
       </c>
       <c r="D7" s="20">
@@ -2288,7 +2664,7 @@
         <v/>
       </c>
       <c r="E7" s="19">
-        <f>C7+D7</f>
+        <f>C7/2+D7</f>
         <v/>
       </c>
       <c r="F7" s="16">
@@ -2314,7 +2690,7 @@
         <v/>
       </c>
       <c r="C8" s="19">
-        <f>0.5*'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B8,0.000000001)</f>
+        <f>'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B8,0.000000001)</f>
         <v/>
       </c>
       <c r="D8" s="20">
@@ -2322,7 +2698,7 @@
         <v/>
       </c>
       <c r="E8" s="19">
-        <f>C8+D8</f>
+        <f>C8/2+D8</f>
         <v/>
       </c>
       <c r="F8" s="16">
@@ -2348,7 +2724,7 @@
         <v/>
       </c>
       <c r="C9" s="19">
-        <f>0.5*'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B9,0.000000001)</f>
+        <f>'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B9,0.000000001)</f>
         <v/>
       </c>
       <c r="D9" s="20">
@@ -2356,7 +2732,7 @@
         <v/>
       </c>
       <c r="E9" s="19">
-        <f>C9+D9</f>
+        <f>C9/2+D9</f>
         <v/>
       </c>
       <c r="F9" s="16">
@@ -2382,7 +2758,7 @@
         <v/>
       </c>
       <c r="C10" s="19">
-        <f>0.5*'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B10,0.000000001)</f>
+        <f>'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B10,0.000000001)</f>
         <v/>
       </c>
       <c r="D10" s="20">
@@ -2390,7 +2766,7 @@
         <v/>
       </c>
       <c r="E10" s="19">
-        <f>C10+D10</f>
+        <f>C10/2+D10</f>
         <v/>
       </c>
       <c r="F10" s="16">
@@ -2416,7 +2792,7 @@
         <v/>
       </c>
       <c r="C11" s="19">
-        <f>0.5*'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B11,0.000000001)</f>
+        <f>'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B11,0.000000001)</f>
         <v/>
       </c>
       <c r="D11" s="20">
@@ -2424,7 +2800,7 @@
         <v/>
       </c>
       <c r="E11" s="19">
-        <f>C11+D11</f>
+        <f>C11/2+D11</f>
         <v/>
       </c>
       <c r="F11" s="16">
@@ -2450,7 +2826,7 @@
         <v/>
       </c>
       <c r="C12" s="19">
-        <f>0.5*'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B12,0.000000001)</f>
+        <f>'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B12,0.000000001)</f>
         <v/>
       </c>
       <c r="D12" s="20">
@@ -2458,7 +2834,7 @@
         <v/>
       </c>
       <c r="E12" s="19">
-        <f>C12+D12</f>
+        <f>C12/2+D12</f>
         <v/>
       </c>
       <c r="F12" s="16">
@@ -2484,7 +2860,7 @@
         <v/>
       </c>
       <c r="C13" s="19">
-        <f>0.5*'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B13,0.000000001)</f>
+        <f>'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B13,0.000000001)</f>
         <v/>
       </c>
       <c r="D13" s="20">
@@ -2492,7 +2868,7 @@
         <v/>
       </c>
       <c r="E13" s="19">
-        <f>C13+D13</f>
+        <f>C13/2+D13</f>
         <v/>
       </c>
       <c r="F13" s="16">
@@ -2518,7 +2894,7 @@
         <v/>
       </c>
       <c r="C14" s="19">
-        <f>0.5*'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B14,0.000000001)</f>
+        <f>'0_Inputs'!$B$10*('0_Inputs'!$B$39/0.01)*'0_Inputs'!$B$21/MAX(B14,0.000000001)</f>
         <v/>
       </c>
       <c r="D14" s="20">
@@ -2526,7 +2902,7 @@
         <v/>
       </c>
       <c r="E14" s="19">
-        <f>C14+D14</f>
+        <f>C14/2+D14</f>
         <v/>
       </c>
       <c r="F14" s="16">
@@ -2540,6 +2916,20 @@
       <c r="H14" s="21">
         <f>2*E14</f>
         <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>INTEGRAL convention: the trader pays the AVERAGE price along the path (= half the full-size impact),</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t>NOT the post-execution price on the whole size. The impact half is a PRICE PATH, not LP revenue.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3164,7 +3554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3365,7 +3755,7 @@
     <row r="23">
       <c r="A23" s="30" t="inlineStr">
         <is>
-          <t>sell slippage s_s</t>
+          <t>sell slippage s_s (INTEGRAL = half of full)</t>
         </is>
       </c>
       <c r="B23" s="19">
@@ -3398,7 +3788,7 @@
     <row r="26">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>buy slippage s_b</t>
+          <t>buy slippage s_b (INTEGRAL)</t>
         </is>
       </c>
       <c r="B26" s="19">
@@ -3431,10 +3821,21 @@
     <row r="29">
       <c r="A29" s="30" t="inlineStr">
         <is>
-          <t>LP revenue this swap (BTC)</t>
+          <t>LP revenue this swap = FEE ONLY (impact is a price path, not revenue)</t>
         </is>
       </c>
       <c r="B29" s="32">
+        <f>$B$6*B15*'0_Inputs'!$B$11+B27*B20*'0_Inputs'!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>(endpoint-convention revenue, for reference — the OLD overstated figure)</t>
+        </is>
+      </c>
+      <c r="B30" s="11">
         <f>$B$6*B15-B27*B20</f>
         <v/>
       </c>
@@ -3494,6 +3895,13 @@
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>A swap moves kappa -&gt; the wings re-scale -&gt; every strike re-prices. Level/shape (Sbar,a,gam) do NOT move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="45" t="inlineStr">
+        <is>
+          <t>Impact moves the price along the path; the trader pays the integral. It is NOT captured as LP revenue.</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4103,19 +4511,19 @@
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>revenue/yr (fee+impact, BTC)</t>
+          <t>revenue/yr = FEE x VOLUME only (BTC)</t>
         </is>
       </c>
       <c r="B6" s="16">
-        <f>B4*('0_Inputs'!$B$11+'2_Quote'!$E$9)*'0_Inputs'!$B$38*365*'0_Inputs'!$B$39*'0_Inputs'!$B$9*'2_Quote'!$B$9</f>
+        <f>B4*'0_Inputs'!$B$11*'0_Inputs'!$B$38*365*'5_Portfolio'!$E$9</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>C4*('0_Inputs'!$B$11+'2_Quote'!$E$9)*'0_Inputs'!$B$38*365*'0_Inputs'!$B$39*'0_Inputs'!$B$9*'2_Quote'!$B$9</f>
+        <f>C4*'0_Inputs'!$B$11*'0_Inputs'!$B$38*365*'5_Portfolio'!$E$9</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>D4*('0_Inputs'!$B$11+'2_Quote'!$E$9)*'0_Inputs'!$B$38*365*'0_Inputs'!$B$39*'0_Inputs'!$B$9*'2_Quote'!$B$9</f>
+        <f>D4*'0_Inputs'!$B$11*'0_Inputs'!$B$38*365*'5_Portfolio'!$E$9</f>
         <v/>
       </c>
       <c r="E6" s="16">
@@ -4272,6 +4680,13 @@
       <c r="A15" s="45" t="inlineStr">
         <is>
           <t>NOTE: an LP concentrated in the wings faces a HIGHER Gtilde than this mean; per-LP strike mix is the next refinement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="inlineStr">
+        <is>
+          <t>Revenue is fee x VOLUME. Trade SIZE does not enter (integral convention). Impact is not revenue.</t>
         </is>
       </c>
     </row>
